--- a/ts_forecast_result.xlsx
+++ b/ts_forecast_result.xlsx
@@ -13,7 +13,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="留出段预测" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="预测区间" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模型对比" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="走势图" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SES平滑值" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="走势图" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1776,17 +1777,17 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>α = 0.3, S(T−1) = 136.5789（训练段均值）</t>
+          <t>α = 0.3, S0 = 136.5789（前 19 期实际值的平均）</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>S_(t+1) = α·Y_t + (1−α)·S_t    （S_t 为第 t 期预测值）</t>
+          <t>S_t = α·Y_t + (1−α)·S_(t−1)；  第 t 期预测值 = S_(t−1)</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>S(T−1) 为第 T−1 期的预测值（手动指定或取训练段实际值的平均值）：第 T 期预测值 = α×(第 T−1 期实际值)+(1−α)×S(T−1)，之后逐期递推</t>
+          <t>S0 为初始值（手动指定，或取前若干期实际值的平均值）：从 S0 出发用 Y1, Y2, ... 逐期递推得到 S1, S2, ...；第 t 期的预测值取 S_(t−1)</t>
         </is>
       </c>
     </row>
@@ -1925,8 +1926,12 @@
       </c>
       <c r="E5" s="4" t="n"/>
       <c r="F5" s="4" t="n"/>
-      <c r="G5" s="4" t="n"/>
-      <c r="H5" s="4" t="n"/>
+      <c r="G5" s="5" t="n">
+        <v>136.578947368421</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>-24.57894736842104</v>
+      </c>
       <c r="I5" s="4" t="n"/>
       <c r="J5" s="4" t="n"/>
     </row>
@@ -1947,8 +1952,12 @@
       </c>
       <c r="E6" s="4" t="n"/>
       <c r="F6" s="4" t="n"/>
-      <c r="G6" s="4" t="n"/>
-      <c r="H6" s="4" t="n"/>
+      <c r="G6" s="5" t="n">
+        <v>129.2052631578947</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>-11.20526315789473</v>
+      </c>
       <c r="I6" s="5" t="n">
         <v>112</v>
       </c>
@@ -1973,8 +1982,12 @@
       </c>
       <c r="E7" s="4" t="n"/>
       <c r="F7" s="4" t="n"/>
-      <c r="G7" s="4" t="n"/>
-      <c r="H7" s="4" t="n"/>
+      <c r="G7" s="5" t="n">
+        <v>125.8436842105263</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>-16.84368421052631</v>
+      </c>
       <c r="I7" s="5" t="n">
         <v>118</v>
       </c>
@@ -2003,8 +2016,12 @@
       <c r="F8" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="G8" s="4" t="n"/>
-      <c r="H8" s="4" t="n"/>
+      <c r="G8" s="5" t="n">
+        <v>120.7905789473684</v>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>0.2094210526315976</v>
+      </c>
       <c r="I8" s="5" t="n">
         <v>109</v>
       </c>
@@ -2033,8 +2050,12 @@
       <c r="F9" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="G9" s="4" t="n"/>
-      <c r="H9" s="4" t="n"/>
+      <c r="G9" s="5" t="n">
+        <v>120.8534052631579</v>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>4.146594736842133</v>
+      </c>
       <c r="I9" s="5" t="n">
         <v>121</v>
       </c>
@@ -2063,8 +2084,12 @@
       <c r="F10" s="5" t="n">
         <v>-1.333333333333329</v>
       </c>
-      <c r="G10" s="4" t="n"/>
-      <c r="H10" s="4" t="n"/>
+      <c r="G10" s="5" t="n">
+        <v>122.0973836842105</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>-5.097383684210499</v>
+      </c>
       <c r="I10" s="5" t="n">
         <v>125</v>
       </c>
@@ -2093,8 +2118,12 @@
       <c r="F11" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="G11" s="4" t="n"/>
-      <c r="H11" s="4" t="n"/>
+      <c r="G11" s="5" t="n">
+        <v>120.5681685789473</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>9.431831421052664</v>
+      </c>
       <c r="I11" s="5" t="n">
         <v>117</v>
       </c>
@@ -2123,8 +2152,12 @@
       <c r="F12" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="G12" s="4" t="n"/>
-      <c r="H12" s="4" t="n"/>
+      <c r="G12" s="5" t="n">
+        <v>123.3977180052631</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>4.60228199473687</v>
+      </c>
       <c r="I12" s="5" t="n">
         <v>130</v>
       </c>
@@ -2153,8 +2186,12 @@
       <c r="F13" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="G13" s="4" t="n"/>
-      <c r="H13" s="4" t="n"/>
+      <c r="G13" s="5" t="n">
+        <v>124.7784026036842</v>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>12.22159739631581</v>
+      </c>
       <c r="I13" s="5" t="n">
         <v>128</v>
       </c>
@@ -2183,8 +2220,12 @@
       <c r="F14" s="5" t="n">
         <v>2.333333333333343</v>
       </c>
-      <c r="G14" s="4" t="n"/>
-      <c r="H14" s="4" t="n"/>
+      <c r="G14" s="5" t="n">
+        <v>128.4448818225789</v>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>5.555118177421065</v>
+      </c>
       <c r="I14" s="5" t="n">
         <v>137</v>
       </c>
@@ -2213,8 +2254,12 @@
       <c r="F15" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="G15" s="4" t="n"/>
-      <c r="H15" s="4" t="n"/>
+      <c r="G15" s="5" t="n">
+        <v>130.1114172758053</v>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>10.88858272419475</v>
+      </c>
       <c r="I15" s="5" t="n">
         <v>134</v>
       </c>
@@ -2243,8 +2288,12 @@
       <c r="F16" s="5" t="n">
         <v>8.666666666666657</v>
       </c>
-      <c r="G16" s="4" t="n"/>
-      <c r="H16" s="4" t="n"/>
+      <c r="G16" s="5" t="n">
+        <v>133.3779920930637</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>12.62200790693635</v>
+      </c>
       <c r="I16" s="5" t="n">
         <v>141</v>
       </c>
@@ -2273,8 +2322,12 @@
       <c r="F17" s="5" t="n">
         <v>-1.333333333333343</v>
       </c>
-      <c r="G17" s="4" t="n"/>
-      <c r="H17" s="4" t="n"/>
+      <c r="G17" s="5" t="n">
+        <v>137.1645944651445</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>1.835405534855454</v>
+      </c>
       <c r="I17" s="5" t="n">
         <v>146</v>
       </c>
@@ -2303,8 +2356,12 @@
       <c r="F18" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="G18" s="4" t="n"/>
-      <c r="H18" s="4" t="n"/>
+      <c r="G18" s="5" t="n">
+        <v>137.7152161256012</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>14.28478387439884</v>
+      </c>
       <c r="I18" s="5" t="n">
         <v>139</v>
       </c>
@@ -2333,8 +2390,12 @@
       <c r="F19" s="5" t="n">
         <v>2.333333333333343</v>
       </c>
-      <c r="G19" s="4" t="n"/>
-      <c r="H19" s="4" t="n"/>
+      <c r="G19" s="5" t="n">
+        <v>142.0006512879208</v>
+      </c>
+      <c r="H19" s="5" t="n">
+        <v>5.999348712079183</v>
+      </c>
       <c r="I19" s="5" t="n">
         <v>152</v>
       </c>
@@ -2363,8 +2424,12 @@
       <c r="F20" s="5" t="n">
         <v>10.66666666666666</v>
       </c>
-      <c r="G20" s="4" t="n"/>
-      <c r="H20" s="4" t="n"/>
+      <c r="G20" s="5" t="n">
+        <v>143.8004559015446</v>
+      </c>
+      <c r="H20" s="5" t="n">
+        <v>13.19954409845545</v>
+      </c>
       <c r="I20" s="5" t="n">
         <v>148</v>
       </c>
@@ -2393,8 +2458,12 @@
       <c r="F21" s="5" t="n">
         <v>8.666666666666657</v>
       </c>
-      <c r="G21" s="4" t="n"/>
-      <c r="H21" s="4" t="n"/>
+      <c r="G21" s="5" t="n">
+        <v>147.7603191310812</v>
+      </c>
+      <c r="H21" s="5" t="n">
+        <v>13.23968086891881</v>
+      </c>
       <c r="I21" s="5" t="n">
         <v>157</v>
       </c>
@@ -2423,8 +2492,12 @@
       <c r="F22" s="5" t="n">
         <v>-1.333333333333343</v>
       </c>
-      <c r="G22" s="4" t="n"/>
-      <c r="H22" s="4" t="n"/>
+      <c r="G22" s="5" t="n">
+        <v>151.7322233917568</v>
+      </c>
+      <c r="H22" s="5" t="n">
+        <v>2.267776608243196</v>
+      </c>
       <c r="I22" s="5" t="n">
         <v>161</v>
       </c>
@@ -2453,8 +2526,12 @@
       <c r="F23" s="5" t="n">
         <v>8.666666666666657</v>
       </c>
-      <c r="G23" s="4" t="n"/>
-      <c r="H23" s="4" t="n"/>
+      <c r="G23" s="5" t="n">
+        <v>152.4125563742298</v>
+      </c>
+      <c r="H23" s="5" t="n">
+        <v>13.58744362577025</v>
+      </c>
       <c r="I23" s="5" t="n">
         <v>154</v>
       </c>
@@ -2581,10 +2658,10 @@
         <v>2.666666666666657</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>145.4052631578947</v>
+        <v>156.4887894619608</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>17.59473684210528</v>
+        <v>6.511210538039165</v>
       </c>
       <c r="I5" s="5" t="n">
         <v>166</v>
@@ -2615,10 +2692,10 @@
         <v>11.66666666666666</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>150.6836842105263</v>
+        <v>158.4421526233726</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>21.31631578947369</v>
+        <v>13.55784737662742</v>
       </c>
       <c r="I6" s="5" t="n">
         <v>163</v>
@@ -2649,10 +2726,10 @@
         <v>14.66666666666666</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>157.0785789473684</v>
+        <v>162.5095068363608</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>17.92142105263159</v>
+        <v>12.4904931636392</v>
       </c>
       <c r="I7" s="5" t="n">
         <v>172</v>
@@ -2683,10 +2760,10 @@
         <v>8.666666666666657</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>162.4550052631579</v>
+        <v>166.2566547854526</v>
       </c>
       <c r="H8" s="5" t="n">
-        <v>6.544994736842114</v>
+        <v>2.743345214547446</v>
       </c>
       <c r="I8" s="5" t="n">
         <v>175</v>
@@ -2717,10 +2794,10 @@
         <v>20.66666666666666</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>164.4185036842105</v>
+        <v>167.0796583498168</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>16.58149631578948</v>
+        <v>13.92034165018322</v>
       </c>
       <c r="I9" s="5" t="n">
         <v>169</v>
@@ -2868,13 +2945,13 @@
         <v>186.0463212172266</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>18.72778945912357</v>
+        <v>12.07813481309841</v>
       </c>
       <c r="I5" s="5" t="n">
-        <v>108.6994703079637</v>
+        <v>132.8160802278686</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>182.1110560078258</v>
+        <v>180.1614986960531</v>
       </c>
       <c r="K5" s="5" t="n">
         <v>7.469939758793239</v>
@@ -2911,13 +2988,13 @@
         <v>186.0463212172266</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>18.72778945912357</v>
+        <v>12.07813481309841</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>113.9778913605953</v>
+        <v>134.7694433892803</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>187.3894770604574</v>
+        <v>182.1148618574649</v>
       </c>
       <c r="K6" s="5" t="n">
         <v>7.469939758793239</v>
@@ -2954,13 +3031,13 @@
         <v>186.0463212172266</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>18.72778945912357</v>
+        <v>12.07813481309841</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>120.3727860974374</v>
+        <v>138.8367976022685</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>193.7843717972995</v>
+        <v>186.1822160704531</v>
       </c>
       <c r="K7" s="5" t="n">
         <v>7.469939758793239</v>
@@ -2997,13 +3074,13 @@
         <v>186.0463212172266</v>
       </c>
       <c r="H8" s="5" t="n">
-        <v>18.72778945912357</v>
+        <v>12.07813481309841</v>
       </c>
       <c r="I8" s="5" t="n">
-        <v>125.7492124132268</v>
+        <v>142.5839455513603</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>199.1607981130889</v>
+        <v>189.9293640195448</v>
       </c>
       <c r="K8" s="5" t="n">
         <v>7.469939758793239</v>
@@ -3040,13 +3117,13 @@
         <v>186.0463212172266</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>18.72778945912357</v>
+        <v>12.07813481309841</v>
       </c>
       <c r="I9" s="5" t="n">
-        <v>127.7127108342795</v>
+        <v>143.4069491157245</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>201.1242965341416</v>
+        <v>190.7523675839091</v>
       </c>
       <c r="K9" s="5" t="n">
         <v>7.469939758793239</v>
@@ -3234,32 +3311,32 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>α = 0.3, S(T−1) = 136.5789（训练段均值）</t>
+          <t>α = 0.3, S0 = 136.5789（前 19 期实际值的平均）</t>
         </is>
       </c>
       <c r="C7" s="4" t="n">
         <v>5</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>1402.92039210104</v>
+        <v>583.525362253519</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>280.584078420208</v>
+        <v>116.7050724507038</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>16.75064411956173</v>
+        <v>10.8030121933979</v>
       </c>
       <c r="G7" s="4" t="n">
         <v>4</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>18.72778945912357</v>
+        <v>12.07813481309841</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>0.0510261485638053</v>
+        <v>0.0323140005608356</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>2.24240685473316</v>
+        <v>1.446198034017763</v>
       </c>
     </row>
     <row r="8">
@@ -3343,6 +3420,649 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E29"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="20" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>SES 递推全过程：S0 ~ S24</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="16" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>S_t = α·Y_t + (1−α)·S_(t−1)；第 t 期的预测值取 S_(t−1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>平滑值</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>计算依据</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>该期实际值</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>数值</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>用作</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>S0</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>初始值</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>136.578947368421</v>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>第 1 期预测值</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>S1</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>α·Y1 + (1−α)·S0</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>112</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>129.2052631578947</v>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>第 2 期预测值</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>α·Y2 + (1−α)·S1</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>118</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>125.8436842105263</v>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>第 3 期预测值</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>S3</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>α·Y3 + (1−α)·S2</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>109</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>120.7905789473684</v>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>第 4 期预测值</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>S4</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>α·Y4 + (1−α)·S3</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>121</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>120.8534052631579</v>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>第 5 期预测值</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>S5</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>α·Y5 + (1−α)·S4</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>125</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>122.0973836842105</v>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>第 6 期预测值</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>S6</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>α·Y6 + (1−α)·S5</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>117</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>120.5681685789473</v>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>第 7 期预测值</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>S7</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>α·Y7 + (1−α)·S6</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>130</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>123.3977180052631</v>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>第 8 期预测值</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>S8</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>α·Y8 + (1−α)·S7</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>128</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>124.7784026036842</v>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>第 9 期预测值</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>S9</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>α·Y9 + (1−α)·S8</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>137</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>128.4448818225789</v>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>第 10 期预测值</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>S10</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>α·Y10 + (1−α)·S9</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>134</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>130.1114172758053</v>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>第 11 期预测值</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>S11</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>α·Y11 + (1−α)·S10</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>141</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>133.3779920930637</v>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>第 12 期预测值</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>α·Y12 + (1−α)·S11</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>146</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>137.1645944651445</v>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>第 13 期预测值</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>S13</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>α·Y13 + (1−α)·S12</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>139</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>137.7152161256012</v>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>第 14 期预测值</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>S14</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>α·Y14 + (1−α)·S13</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>152</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>142.0006512879208</v>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>第 15 期预测值</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>S15</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>α·Y15 + (1−α)·S14</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>148</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>143.8004559015446</v>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>第 16 期预测值</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>S16</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>α·Y16 + (1−α)·S15</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>157</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>147.7603191310812</v>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>第 17 期预测值</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>S17</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>α·Y17 + (1−α)·S16</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>161</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>151.7322233917568</v>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>第 18 期预测值</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>S18</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>α·Y18 + (1−α)·S17</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>154</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>152.4125563742298</v>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>第 19 期预测值</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>S19</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>α·Y19 + (1−α)·S18</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>166</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>156.4887894619608</v>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>第 20 期预测值</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>S20</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>α·Y20 + (1−α)·S19</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="n">
+        <v>163</v>
+      </c>
+      <c r="D25" s="5" t="n">
+        <v>158.4421526233726</v>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>第 21 期预测值</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>S21</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>α·Y21 + (1−α)·S20</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="n">
+        <v>172</v>
+      </c>
+      <c r="D26" s="5" t="n">
+        <v>162.5095068363608</v>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>第 22 期预测值</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>S22</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>α·Y22 + (1−α)·S21</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="n">
+        <v>175</v>
+      </c>
+      <c r="D27" s="5" t="n">
+        <v>166.2566547854526</v>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>第 23 期预测值</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>S23</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>α·Y23 + (1−α)·S22</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="n">
+        <v>169</v>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>167.0796583498168</v>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>第 24 期预测值</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>S24</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>α·Y24 + (1−α)·S23</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="n">
+        <v>181</v>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>171.2557608448717</v>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3532,7 +4252,7 @@
         <v>160.3333333333333</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>145.4052631578947</v>
+        <v>156.4887894619608</v>
       </c>
       <c r="F12" s="5" t="n">
         <v>166</v>
@@ -3552,7 +4272,7 @@
         <v>160.3333333333333</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>150.6836842105263</v>
+        <v>158.4421526233726</v>
       </c>
       <c r="F13" s="5" t="n">
         <v>163</v>
@@ -3572,7 +4292,7 @@
         <v>160.3333333333333</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>157.0785789473684</v>
+        <v>162.5095068363608</v>
       </c>
       <c r="F14" s="5" t="n">
         <v>172</v>
@@ -3592,7 +4312,7 @@
         <v>160.3333333333333</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>162.4550052631579</v>
+        <v>166.2566547854526</v>
       </c>
       <c r="F15" s="5" t="n">
         <v>175</v>
@@ -3612,7 +4332,7 @@
         <v>160.3333333333333</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>164.4185036842105</v>
+        <v>167.0796583498168</v>
       </c>
       <c r="F16" s="5" t="n">
         <v>169</v>
